--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Correlation Field Settings</t>
+          <t>User Deactivation Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ticket Management</t>
+          <t>ServiceNow Catalog Managemnet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>h_01KJCDN74HG92YZHGJTFJP07P4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCDN74HG92YZHGJTFJP07P4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>ServiceNow Field Management</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJCDN74HDBP127E2MW5GFTAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCDN74HDBP127E2MW5GFTAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>User Provisioning Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,142 +913,230 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KJCCA2T0CNRDXW9K2P8FSDCB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCCA2T0CNRDXW9K2P8FSDCB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Correlation Field Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Ticket Management</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCDN74HG92YZHGJTFJP07P4</t>
+          <t>h_01KJCH136KQ6WY0T84CCNSMQ0P</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCDN74HG92YZHGJTFJP07P4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCH136KQ6WY0T84CCNSMQ0P</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCDN74HDBP127E2MW5GFTAR</t>
+          <t>h_01KJCH136KGNMQNHFB9J7WEK7N</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCDN74HDBP127E2MW5GFTAR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCH136KGNMQNHFB9J7WEK7N</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCH136KQ6WY0T84CCNSMQ0P</t>
+          <t>h_01KJCM2DRJC4KG5PBFMX2BPK9C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCH136KQ6WY0T84CCNSMQ0P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCM2DRJC4KG5PBFMX2BPK9C</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCH136KGNMQNHFB9J7WEK7N</t>
+          <t>h_01KJCM2DRJ4R7HP8NM8BPJ0TWD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCH136KGNMQNHFB9J7WEK7N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCM2DRJ4R7HP8NM8BPJ0TWD</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCM2DRJC4KG5PBFMX2BPK9C</t>
+          <t>h_01KJCPMAPZB9YYHQHZH5T4SMFB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCM2DRJC4KG5PBFMX2BPK9C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCPMAPZB9YYHQHZH5T4SMFB</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCM2DRJ4R7HP8NM8BPJ0TWD</t>
+          <t>h_01KJCPMAPZBZE3YB185FXRPJCG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCM2DRJ4R7HP8NM8BPJ0TWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCPMAPZBZE3YB185FXRPJCG</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -991,51 +991,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,32 +1111,54 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JML Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K35A8BW0AFVC2DSAZHQQXN72</t>
+          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K35A8BW0AFVC2DSAZHQQXN72</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Creation Settings</t>
+          <t>User Provisioning Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
+          <t>h_01K35A8BW0AFVC2DSAZHQQXN72</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K35A8BW0AFVC2DSAZHQQXN72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>User Creation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
+          <t>h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>ServiceNow Catalog Managemnet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJC7ZTQER171YSQ2EMR33WXF</t>
+          <t>h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7ZTQER171YSQ2EMR33WXF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Updation Settings</t>
+          <t>ServiceNow Field Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>h_01KJC7ZTQER171YSQ2EMR33WXF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7ZTQER171YSQ2EMR33WXF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>User Updation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYZCE2SVDX8MAF5K15</t>
+          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYZCE2SVDX8MAF5K15</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>ServiceNow Catalog Managemnet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYAK8T56FB4PEQYH77</t>
+          <t>h_01KJCACEEYZCE2SVDX8MAF5K15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYAK8T56FB4PEQYH77</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYZCE2SVDX8MAF5K15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>User Deactivation Settings</t>
+          <t>ServiceNow Field Management</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>h_01KJCACEEYAK8T56FB4PEQYH77</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYAK8T56FB4PEQYH77</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>User Deactivation Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCPMAPZB9YYHQHZH5T4SMFB</t>
+          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCPMAPZB9YYHQHZH5T4SMFB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>ServiceNow Catalog Managemnet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCPMAPZBZE3YB185FXRPJCG</t>
+          <t>h_01KJCVV7XK4RGRBA6PRP2ATA2Y</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCPMAPZBZE3YB185FXRPJCG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCVV7XK4RGRBA6PRP2ATA2Y</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>User Provisioning Settings</t>
+          <t>ServiceNow Field Management</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJCCA2T0CNRDXW9K2P8FSDCB</t>
+          <t>h_01KJCVV7XKPCY9JZ81078MD4B8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCCA2T0CNRDXW9K2P8FSDCB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCVV7XKPCY9JZ81078MD4B8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Correlation Field Settings</t>
+          <t>Ticket Management</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ticket Management</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,63 +979,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,32 +1133,10 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,63 +979,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,32 +1111,54 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KJPP3N9KEVWF58C06Q6K69M5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPP3N9KEVWF58C06Q6K69M5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,32 +1133,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJPP3N9KEVWF58C06Q6K69M5</t>
+          <t>h_01KJQ0BX1QBDDTX2BZE5FWJD5H</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPP3N9KEVWF58C06Q6K69M5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQ0BX1QBDDTX2BZE5FWJD5H</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJQ0BX1QBDDTX2BZE5FWJD5H</t>
+          <t>h_01KJQ88C4B9FY7TF5ZR8CWJNT2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQ0BX1QBDDTX2BZE5FWJD5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQ88C4B9FY7TF5ZR8CWJNT2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,32 +1155,10 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJQ88C4B9FY7TF5ZR8CWJNT2</t>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQ88C4B9FY7TF5ZR8CWJNT2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,29 +969,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Generate sAMAccountName</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01KJS5N2ZY04EST2JJY74F72F8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS5N2ZY04EST2JJY74F72F8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,76 +1089,120 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generate sAMAccountName</t>
+          <t>Generate sAMAccount Name</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -991,218 +991,306 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJS5N2ZY04EST2JJY74F72F8</t>
+          <t>h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS5N2ZY04EST2JJY74F72F8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Generate User Principal Name (UPN)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Generate Proxy Address</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KJS9PTTBJ77VMMMMW19467TA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS9PTTBJ77VMMMMW19467TA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJS9PTTBJ77VMMMMW19467TA</t>
+          <t>h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS9PTTBJ77VMMMMW19467TA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,41 +1155,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,41 +1221,41 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,32 +1265,54 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,7 +1211,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Group Assignment Rules</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,41 +1243,41 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,32 +1287,54 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,51 +749,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>User Updation Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
+          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7FTH92XXEX1F34Y4S0ZP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>User Deactivation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJC7ZTQER171YSQ2EMR33WXF</t>
+          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC7ZTQER171YSQ2EMR33WXF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>User Updation Settings</t>
+          <t>Ticket Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,63 +803,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYZCE2SVDX8MAF5K15</t>
+          <t>h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYZCE2SVDX8MAF5K15</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>Generate sAMAccount Name</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYAK8T56FB4PEQYH77</t>
+          <t>h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEYAK8T56FB4PEQYH77</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>User Deactivation Settings</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,63 +869,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ServiceNow Catalog Managemnet</t>
+          <t>Generate User Principal Name (UPN)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCVV7XK4RGRBA6PRP2ATA2Y</t>
+          <t>h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCVV7XK4RGRBA6PRP2ATA2Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ServiceNow Field Management</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJCVV7XKPCY9JZ81078MD4B8</t>
+          <t>h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCVV7XKPCY9JZ81078MD4B8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ticket Management</t>
+          <t>Generate Proxy Address</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Naming Policy</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,384 +957,252 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJSG4251V483NS6N0BBFS9KP</t>
+          <t>h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG4251V483NS6N0BBFS9KP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generate sAMAccount Name</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
+          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generate Common Name (CN)</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Generate User Principal Name (UPN)</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJS819S47H9Q0P73V6HZKMCV</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS819S47H9Q0P73V6HZKMCV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Generate Email</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Generate Proxy Address</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Group Assignment Rules</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
+          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Group Assignment Rules</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Attribute Map</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ticket Management</t>
+          <t>Manager Mapping Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>h_01KMD6WMEJAEPJZRRT60NCHXAM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJC8AY4E9JBWPM5N5JN34AZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KMD6WMEJAEPJZRRT60NCHXAM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Naming Policy</t>
+          <t>Future Hire Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJSG4251V483NS6N0BBFS9KP</t>
+          <t>h_01KMD70678KJ57FAQ7W2FBCAZY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG4251V483NS6N0BBFS9KP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KMD70678KJ57FAQ7W2FBCAZY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Generate sAMAccount Name</t>
+          <t>Inactive User Discovery Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
+          <t>h_01KMD73YA4D0AECSBBRHMJY2N7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KMD73YA4D0AECSBBRHMJY2N7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Generate Common Name (CN)</t>
+          <t>Inactive User Management Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
+          <t>h_01KMD7419Z4SKADMAFVDTE4YTE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KMD7419Z4SKADMAFVDTE4YTE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Generate User Principal Name (UPN)</t>
+          <t>User Deletion Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJS819S47H9Q0P73V6HZKMCV</t>
+          <t>h_01KMD7445RKSVRCMZV5F9GWGMW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS819S47H9Q0P73V6HZKMCV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KMD7445RKSVRCMZV5F9GWGMW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Generate Email</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
+          <t>h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG4251V483NS6N0BBFS9KP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Generate Proxy Address</t>
+          <t>Generate sAMAccount Name</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,107 +935,107 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
+          <t>h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS35S7NDZ6Q5HTCPCM8TWQH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
+          <t>h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7B0KYNC8TVV0MRA6HVNMB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Generate User Principal Name (UPN)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS819S47H9Q0P73V6HZKMCV</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS7VTF1PS4HNNKQ8DN5NH1Q</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Generate Proxy Address</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJS952MW19Q1P6BM2CZ0MSK1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,164 +1045,252 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSD1S2JWXMP985BXBJ7Q4PM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Group Assignment Rules</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>OU Assignment Rules</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Group Assignment Rules</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Active-Directory-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
